--- a/mainWidget/mainWidget/src/database/admin/壳体物性材料.xlsx
+++ b/mainWidget/mainWidget/src/database/admin/壳体物性材料.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>序号</t>
   </si>
@@ -32,6 +32,21 @@
   </si>
   <si>
     <t>导热系数W/(m·K)</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>测试</t>
+  </si>
+  <si>
+    <t>4882.5</t>
+  </si>
+  <si>
+    <t>736</t>
+  </si>
+  <si>
+    <t>81</t>
   </si>
 </sst>
 </file>
@@ -359,7 +374,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -382,6 +397,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>